--- a/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_74_R8.xlsx
+++ b/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_74_R8.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>7.3102</v>
+        <v>8.1181</v>
       </c>
       <c r="E2" t="n">
-        <v>3.989</v>
+        <v>4.4609</v>
       </c>
       <c r="F2" t="n">
-        <v>3.3212</v>
+        <v>3.6573</v>
       </c>
       <c r="G2" t="n">
         <v>7.563</v>
@@ -610,13 +610,13 @@
         <v>1.3917</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.3971</v>
+        <v>0.4107</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.5895</v>
+        <v>-0.1177</v>
       </c>
       <c r="U2" t="n">
-        <v>0.1924</v>
+        <v>0.5285</v>
       </c>
       <c r="V2" t="n">
         <v>1.0722</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>6.3742</v>
+        <v>6.3988</v>
       </c>
       <c r="E3" t="n">
-        <v>0.6771</v>
+        <v>0.8698</v>
       </c>
       <c r="F3" t="n">
-        <v>5.6971</v>
+        <v>5.529</v>
       </c>
       <c r="G3" t="n">
         <v>5.1144</v>
@@ -688,13 +688,13 @@
         <v>1.8556</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.7376</v>
+        <v>-0.713</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.5975</v>
+        <v>-0.4048</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.1401</v>
+        <v>-0.3082</v>
       </c>
       <c r="V3" t="n">
         <v>0.1418</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>5.9345</v>
+        <v>5.4385</v>
       </c>
       <c r="E4" t="n">
-        <v>0.1163</v>
+        <v>0.4269</v>
       </c>
       <c r="F4" t="n">
-        <v>5.8181</v>
+        <v>5.0116</v>
       </c>
       <c r="G4" t="n">
         <v>6.6837</v>
@@ -766,13 +766,13 @@
         <v>1.8556</v>
       </c>
       <c r="S4" t="n">
-        <v>0.3383</v>
+        <v>-0.1577</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.5895</v>
+        <v>-0.279</v>
       </c>
       <c r="U4" t="n">
-        <v>0.9278</v>
+        <v>0.1213</v>
       </c>
       <c r="V4" t="n">
         <v>0.5361</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>4.5066</v>
+        <v>4.093</v>
       </c>
       <c r="E5" t="n">
-        <v>3.6195</v>
+        <v>3.3403</v>
       </c>
       <c r="F5" t="n">
-        <v>0.8871</v>
+        <v>0.7527</v>
       </c>
       <c r="G5" t="n">
         <v>4.9553</v>
@@ -844,13 +844,13 @@
         <v>1.1598</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.3611</v>
+        <v>-0.7747000000000001</v>
       </c>
       <c r="T5" t="n">
-        <v>0.0474</v>
+        <v>-0.2317</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.4085</v>
+        <v>-0.543</v>
       </c>
       <c r="V5" t="n">
         <v>1.0722</v>
@@ -877,10 +877,10 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>3.5214</v>
+        <v>3.2855</v>
       </c>
       <c r="E6" t="n">
-        <v>2.8324</v>
+        <v>2.5965</v>
       </c>
       <c r="F6" t="n">
         <v>0.6889</v>
@@ -922,10 +922,10 @@
         <v>0.6959</v>
       </c>
       <c r="S6" t="n">
-        <v>0.3145</v>
+        <v>0.0786</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.0351</v>
+        <v>-0.2711</v>
       </c>
       <c r="U6" t="n">
         <v>0.3497</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>1.755</v>
+        <v>2.3434</v>
       </c>
       <c r="E7" t="n">
-        <v>0.0485</v>
+        <v>0.1665</v>
       </c>
       <c r="F7" t="n">
-        <v>1.7064</v>
+        <v>2.1769</v>
       </c>
       <c r="G7" t="n">
         <v>1.6499</v>
@@ -1000,13 +1000,13 @@
         <v>0.9278</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.6808999999999999</v>
+        <v>-0.0925</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.4402</v>
+        <v>-0.3222</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.2407</v>
+        <v>0.2298</v>
       </c>
       <c r="V7" t="n">
         <v>-0.1418</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>1.6419</v>
+        <v>1.43</v>
       </c>
       <c r="E8" t="n">
-        <v>-2.635</v>
+        <v>-2.9141</v>
       </c>
       <c r="F8" t="n">
-        <v>4.2769</v>
+        <v>4.3441</v>
       </c>
       <c r="G8" t="n">
         <v>2.1213</v>
@@ -1078,13 +1078,13 @@
         <v>1.8556</v>
       </c>
       <c r="S8" t="n">
-        <v>0.0721</v>
+        <v>-0.1399</v>
       </c>
       <c r="T8" t="n">
-        <v>0.1968</v>
+        <v>-0.0824</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.1247</v>
+        <v>-0.0575</v>
       </c>
       <c r="V8" t="n">
         <v>1.0722</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.158</v>
+        <v>0.2123</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.2033</v>
+        <v>-0.9674</v>
       </c>
       <c r="F9" t="n">
-        <v>1.0453</v>
+        <v>1.1797</v>
       </c>
       <c r="G9" t="n">
         <v>2.0881</v>
@@ -1156,13 +1156,13 @@
         <v>0.9278</v>
       </c>
       <c r="S9" t="n">
-        <v>-1.5657</v>
+        <v>-1.1953</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.7468</v>
+        <v>-0.5109</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.8188</v>
+        <v>-0.6844</v>
       </c>
       <c r="V9" t="n">
         <v>-1.6083</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.4548</v>
+        <v>-0.6743</v>
       </c>
       <c r="E10" t="n">
-        <v>0.7389</v>
+        <v>0.3851</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.1938</v>
+        <v>-1.0593</v>
       </c>
       <c r="G10" t="n">
         <v>-1.0321</v>
@@ -1234,13 +1234,13 @@
         <v>0.232</v>
       </c>
       <c r="S10" t="n">
-        <v>0.3453</v>
+        <v>0.1259</v>
       </c>
       <c r="T10" t="n">
-        <v>0.4129</v>
+        <v>0.0591</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.0677</v>
+        <v>0.0668</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.9874000000000001</v>
+        <v>-1.3914</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.5281</v>
+        <v>-1.764</v>
       </c>
       <c r="F11" t="n">
-        <v>0.5406</v>
+        <v>0.3726</v>
       </c>
       <c r="G11" t="n">
         <v>-0.9500999999999999</v>
@@ -1312,13 +1312,13 @@
         <v>0.4639</v>
       </c>
       <c r="S11" t="n">
-        <v>0.6585</v>
+        <v>0.2546</v>
       </c>
       <c r="T11" t="n">
-        <v>0.2636</v>
+        <v>0.0277</v>
       </c>
       <c r="U11" t="n">
-        <v>0.3949</v>
+        <v>0.2269</v>
       </c>
       <c r="V11" t="n">
         <v>0</v>
@@ -1345,10 +1345,10 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-2.591</v>
+        <v>-2.5164</v>
       </c>
       <c r="E12" t="n">
-        <v>-2.5342</v>
+        <v>-2.4595</v>
       </c>
       <c r="F12" t="n">
         <v>-0.0568</v>
@@ -1390,10 +1390,10 @@
         <v>0.9278</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.08260000000000001</v>
+        <v>-0.007900000000000001</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.2987</v>
+        <v>-0.224</v>
       </c>
       <c r="U12" t="n">
         <v>0.2161</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-4.7632</v>
+        <v>-4.275</v>
       </c>
       <c r="E13" t="n">
-        <v>-4.8251</v>
+        <v>-4.4712</v>
       </c>
       <c r="F13" t="n">
-        <v>0.0618</v>
+        <v>0.1963</v>
       </c>
       <c r="G13" t="n">
         <v>-3.1545</v>
@@ -1468,13 +1468,13 @@
         <v>0.4639</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.9129</v>
+        <v>-0.4246</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.7468</v>
+        <v>-0.393</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.1661</v>
+        <v>-0.0316</v>
       </c>
       <c r="V13" t="n">
         <v>0</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>22.0894</v>
+        <v>22.4625</v>
       </c>
       <c r="E14" t="n">
-        <v>-0.7040000000000015</v>
+        <v>-0.3301999999999996</v>
       </c>
       <c r="F14" t="n">
-        <v>22.79280000000001</v>
+        <v>22.793</v>
       </c>
       <c r="G14" t="n">
         <v>25.5028</v>
@@ -1546,13 +1546,13 @@
         <v>12.7574</v>
       </c>
       <c r="S14" t="n">
-        <v>-3.0092</v>
+        <v>-2.6358</v>
       </c>
       <c r="T14" t="n">
-        <v>-3.123400000000001</v>
+        <v>-2.75</v>
       </c>
       <c r="U14" t="n">
-        <v>0.1143</v>
+        <v>0.1143999999999999</v>
       </c>
       <c r="V14" t="n">
         <v>3.0748</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>T. HORTON TUCKER</t>
+          <t>O. BITIM</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>3.5537</v>
+        <v>2.9977</v>
       </c>
       <c r="E15" t="n">
-        <v>1.5694</v>
+        <v>2.4093</v>
       </c>
       <c r="F15" t="n">
-        <v>1.9844</v>
+        <v>0.5884</v>
       </c>
       <c r="G15" t="n">
-        <v>-0.4071</v>
+        <v>1.8419</v>
       </c>
       <c r="H15" t="n">
-        <v>-1.886</v>
+        <v>-0.07199999999999999</v>
       </c>
       <c r="I15" t="n">
-        <v>1.4789</v>
+        <v>1.9139</v>
       </c>
       <c r="J15" t="n">
-        <v>0.0828</v>
+        <v>2.6215</v>
       </c>
       <c r="K15" t="n">
-        <v>-1.7674</v>
+        <v>1.1259</v>
       </c>
       <c r="L15" t="n">
-        <v>1.8502</v>
+        <v>1.4956</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.4899</v>
+        <v>-0.7796</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.1186</v>
+        <v>-1.1979</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.3713</v>
+        <v>0.4183</v>
       </c>
       <c r="P15" t="n">
-        <v>2.3195</v>
+        <v>0.6959</v>
       </c>
       <c r="Q15" t="n">
         <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>2.3195</v>
+        <v>0.6959</v>
       </c>
       <c r="S15" t="n">
-        <v>1.7831</v>
+        <v>0.4599</v>
       </c>
       <c r="T15" t="n">
-        <v>1.4866</v>
+        <v>-0.2122</v>
       </c>
       <c r="U15" t="n">
-        <v>0.2965</v>
+        <v>0.6721</v>
       </c>
       <c r="V15" t="n">
-        <v>-0.1418</v>
+        <v>0</v>
       </c>
       <c r="W15" t="n">
         <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>-0.1418</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>O. BITIM</t>
+          <t>T. HORTON TUCKER</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,67 +1657,67 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>3.0306</v>
+        <v>2.9532</v>
       </c>
       <c r="E16" t="n">
-        <v>2.1734</v>
+        <v>0.9796</v>
       </c>
       <c r="F16" t="n">
-        <v>0.8572</v>
+        <v>1.9736</v>
       </c>
       <c r="G16" t="n">
-        <v>1.8419</v>
+        <v>-0.4071</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.07199999999999999</v>
+        <v>-1.886</v>
       </c>
       <c r="I16" t="n">
-        <v>1.9139</v>
+        <v>1.4789</v>
       </c>
       <c r="J16" t="n">
-        <v>2.6215</v>
+        <v>0.0828</v>
       </c>
       <c r="K16" t="n">
-        <v>1.1259</v>
+        <v>-1.7674</v>
       </c>
       <c r="L16" t="n">
-        <v>1.4956</v>
+        <v>1.8502</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.7796</v>
+        <v>-0.4899</v>
       </c>
       <c r="N16" t="n">
-        <v>-1.1979</v>
+        <v>-0.1186</v>
       </c>
       <c r="O16" t="n">
-        <v>0.4183</v>
+        <v>-0.3713</v>
       </c>
       <c r="P16" t="n">
-        <v>0.6959</v>
+        <v>2.3195</v>
       </c>
       <c r="Q16" t="n">
         <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>0.6959</v>
+        <v>2.3195</v>
       </c>
       <c r="S16" t="n">
-        <v>0.4929</v>
+        <v>1.1826</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.4481</v>
+        <v>0.8968</v>
       </c>
       <c r="U16" t="n">
-        <v>0.9409999999999999</v>
+        <v>0.2858</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>-0.1418</v>
       </c>
       <c r="W16" t="n">
         <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>-0.1418</v>
       </c>
     </row>
     <row r="17">
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1.1897</v>
+        <v>1.5093</v>
       </c>
       <c r="E17" t="n">
-        <v>0.0029</v>
+        <v>0.1208</v>
       </c>
       <c r="F17" t="n">
-        <v>1.1868</v>
+        <v>1.3884</v>
       </c>
       <c r="G17" t="n">
         <v>0.5084</v>
@@ -1780,13 +1780,13 @@
         <v>1.1598</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.6203</v>
+        <v>-0.3007</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.2829</v>
+        <v>-0.165</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.3374</v>
+        <v>-0.1357</v>
       </c>
       <c r="V17" t="n">
         <v>0.1418</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.7485000000000001</v>
+        <v>0.4854</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.9739</v>
+        <v>-1.0918</v>
       </c>
       <c r="F18" t="n">
-        <v>1.7224</v>
+        <v>1.5772</v>
       </c>
       <c r="G18" t="n">
         <v>-0.2225</v>
@@ -1858,13 +1858,13 @@
         <v>2.3195</v>
       </c>
       <c r="S18" t="n">
-        <v>0.8834</v>
+        <v>0.6203</v>
       </c>
       <c r="T18" t="n">
-        <v>0.2047</v>
+        <v>0.0868</v>
       </c>
       <c r="U18" t="n">
-        <v>0.6787</v>
+        <v>0.5335</v>
       </c>
       <c r="V18" t="n">
         <v>-1.0722</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.2481</v>
+        <v>-0.6627999999999999</v>
       </c>
       <c r="E19" t="n">
-        <v>-2.4949</v>
+        <v>-2.7308</v>
       </c>
       <c r="F19" t="n">
-        <v>2.2468</v>
+        <v>2.068</v>
       </c>
       <c r="G19" t="n">
         <v>0.149</v>
@@ -1936,13 +1936,13 @@
         <v>1.1598</v>
       </c>
       <c r="S19" t="n">
-        <v>0.7625999999999999</v>
+        <v>0.3479</v>
       </c>
       <c r="T19" t="n">
-        <v>0.1221</v>
+        <v>-0.1138</v>
       </c>
       <c r="U19" t="n">
-        <v>0.6405</v>
+        <v>0.4617</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.9535</v>
+        <v>-1.4753</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.4265</v>
+        <v>-0.7803</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.527</v>
+        <v>-0.695</v>
       </c>
       <c r="G20" t="n">
         <v>-1.2335</v>
@@ -2014,13 +2014,13 @@
         <v>0.9278</v>
       </c>
       <c r="S20" t="n">
-        <v>0.9063</v>
+        <v>0.3844</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.1766</v>
+        <v>-0.5305</v>
       </c>
       <c r="U20" t="n">
-        <v>1.0829</v>
+        <v>0.9147999999999999</v>
       </c>
       <c r="V20" t="n">
         <v>-0.3943</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.8757</v>
+        <v>-2.3874</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.8226</v>
+        <v>-2.4688</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.0531</v>
+        <v>0.0813</v>
       </c>
       <c r="G21" t="n">
         <v>-1.9119</v>
@@ -2092,13 +2092,13 @@
         <v>0.9278</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.7319</v>
+        <v>-0.2436</v>
       </c>
       <c r="T21" t="n">
-        <v>-1.0376</v>
+        <v>-0.6838</v>
       </c>
       <c r="U21" t="n">
-        <v>0.3058</v>
+        <v>0.4402</v>
       </c>
       <c r="V21" t="n">
         <v>0</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-3.2981</v>
+        <v>-2.9614</v>
       </c>
       <c r="E22" t="n">
-        <v>-2.6952</v>
+        <v>-2.4593</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.6029</v>
+        <v>-0.5021</v>
       </c>
       <c r="G22" t="n">
         <v>-3.9459</v>
@@ -2170,13 +2170,13 @@
         <v>0.9278</v>
       </c>
       <c r="S22" t="n">
-        <v>0.2561</v>
+        <v>0.5928</v>
       </c>
       <c r="T22" t="n">
-        <v>0.3462</v>
+        <v>0.5821</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.0901</v>
+        <v>0.0108</v>
       </c>
       <c r="V22" t="n">
         <v>-0.5361</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-4.0043</v>
+        <v>-3.3258</v>
       </c>
       <c r="E23" t="n">
-        <v>-1.9854</v>
+        <v>-1.8674</v>
       </c>
       <c r="F23" t="n">
-        <v>-2.0189</v>
+        <v>-1.4583</v>
       </c>
       <c r="G23" t="n">
         <v>-4.9318</v>
@@ -2248,13 +2248,13 @@
         <v>0.9278</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.9849</v>
+        <v>-0.3064</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.6247</v>
+        <v>-0.5067</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.3602</v>
+        <v>0.2003</v>
       </c>
       <c r="V23" t="n">
         <v>2.1444</v>
@@ -2269,7 +2269,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>D. HALL</t>
+          <t>M. JANTUNEN</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,73 +2281,73 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-5.224</v>
+        <v>-5.2644</v>
       </c>
       <c r="E24" t="n">
-        <v>-5.444</v>
+        <v>-2.8096</v>
       </c>
       <c r="F24" t="n">
-        <v>0.22</v>
+        <v>-2.4548</v>
       </c>
       <c r="G24" t="n">
-        <v>-5.6321</v>
+        <v>-3.5674</v>
       </c>
       <c r="H24" t="n">
-        <v>-3.3768</v>
+        <v>-0.8739</v>
       </c>
       <c r="I24" t="n">
-        <v>-2.2553</v>
+        <v>-2.6935</v>
       </c>
       <c r="J24" t="n">
-        <v>-4.6808</v>
+        <v>-2.0197</v>
       </c>
       <c r="K24" t="n">
-        <v>-2.2715</v>
+        <v>-0.4839</v>
       </c>
       <c r="L24" t="n">
-        <v>-2.4093</v>
+        <v>-1.5359</v>
       </c>
       <c r="M24" t="n">
-        <v>-0.9513</v>
+        <v>-1.5477</v>
       </c>
       <c r="N24" t="n">
-        <v>-1.1053</v>
+        <v>-0.39</v>
       </c>
       <c r="O24" t="n">
-        <v>0.154</v>
+        <v>-1.1577</v>
       </c>
       <c r="P24" t="n">
-        <v>-0.9278</v>
+        <v>-0.232</v>
       </c>
       <c r="Q24" t="n">
-        <v>-3.4793</v>
+        <v>-1.1598</v>
       </c>
       <c r="R24" t="n">
-        <v>2.5515</v>
+        <v>0.9278</v>
       </c>
       <c r="S24" t="n">
-        <v>1.3359</v>
+        <v>0.6794</v>
       </c>
       <c r="T24" t="n">
-        <v>1.6438</v>
+        <v>0.3699</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.3079</v>
+        <v>0.3095</v>
       </c>
       <c r="V24" t="n">
-        <v>0</v>
+        <v>-2.1444</v>
       </c>
       <c r="W24" t="n">
-        <v>1.0722</v>
+        <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>-1.0722</v>
+        <v>-2.1444</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>M. JANTUNEN</t>
+          <t>D. HALL</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2359,67 +2359,67 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-5.5682</v>
+        <v>-5.5621</v>
       </c>
       <c r="E25" t="n">
-        <v>-3.2814</v>
+        <v>-6.1517</v>
       </c>
       <c r="F25" t="n">
-        <v>-2.2867</v>
+        <v>0.5897</v>
       </c>
       <c r="G25" t="n">
-        <v>-3.5674</v>
+        <v>-5.6321</v>
       </c>
       <c r="H25" t="n">
-        <v>-0.8739</v>
+        <v>-3.3768</v>
       </c>
       <c r="I25" t="n">
-        <v>-2.6935</v>
+        <v>-2.2553</v>
       </c>
       <c r="J25" t="n">
-        <v>-2.0197</v>
+        <v>-4.6808</v>
       </c>
       <c r="K25" t="n">
-        <v>-0.4839</v>
+        <v>-2.2715</v>
       </c>
       <c r="L25" t="n">
-        <v>-1.5359</v>
+        <v>-2.4093</v>
       </c>
       <c r="M25" t="n">
-        <v>-1.5477</v>
+        <v>-0.9513</v>
       </c>
       <c r="N25" t="n">
-        <v>-0.39</v>
+        <v>-1.1053</v>
       </c>
       <c r="O25" t="n">
-        <v>-1.1577</v>
+        <v>0.154</v>
       </c>
       <c r="P25" t="n">
-        <v>-0.232</v>
+        <v>-0.9278</v>
       </c>
       <c r="Q25" t="n">
-        <v>-1.1598</v>
+        <v>-3.4793</v>
       </c>
       <c r="R25" t="n">
-        <v>0.9278</v>
+        <v>2.5515</v>
       </c>
       <c r="S25" t="n">
-        <v>0.3756</v>
+        <v>0.9979</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.1019</v>
+        <v>0.9361</v>
       </c>
       <c r="U25" t="n">
-        <v>0.4775</v>
+        <v>0.0617</v>
       </c>
       <c r="V25" t="n">
-        <v>-2.1444</v>
+        <v>0</v>
       </c>
       <c r="W25" t="n">
-        <v>0</v>
+        <v>1.0722</v>
       </c>
       <c r="X25" t="n">
-        <v>-2.1444</v>
+        <v>-1.0722</v>
       </c>
     </row>
     <row r="26">
@@ -2437,13 +2437,13 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-8.4399</v>
+        <v>-7.6092</v>
       </c>
       <c r="E26" t="n">
-        <v>-6.4147</v>
+        <v>-5.9429</v>
       </c>
       <c r="F26" t="n">
-        <v>-2.0253</v>
+        <v>-1.6663</v>
       </c>
       <c r="G26" t="n">
         <v>-6.15</v>
@@ -2482,13 +2482,13 @@
         <v>1.3917</v>
       </c>
       <c r="S26" t="n">
-        <v>-1.4497</v>
+        <v>-0.619</v>
       </c>
       <c r="T26" t="n">
-        <v>-1.2459</v>
+        <v>-0.7741</v>
       </c>
       <c r="U26" t="n">
-        <v>-0.2038</v>
+        <v>0.1551</v>
       </c>
       <c r="V26" t="n">
         <v>-1.0722</v>
@@ -2515,13 +2515,13 @@
         <v>1</v>
       </c>
       <c r="D27" t="n">
-        <v>-22.0893</v>
+        <v>-21.3028</v>
       </c>
       <c r="E27" t="n">
         <v>-22.7929</v>
       </c>
       <c r="F27" t="n">
-        <v>0.7036999999999995</v>
+        <v>1.490100000000002</v>
       </c>
       <c r="G27" t="n">
         <v>-25.5029</v>
@@ -2545,7 +2545,7 @@
         <v>-11.4034</v>
       </c>
       <c r="N27" t="n">
-        <v>-5.0638</v>
+        <v>-5.063800000000001</v>
       </c>
       <c r="O27" t="n">
         <v>-6.339600000000001</v>
@@ -2560,13 +2560,13 @@
         <v>16.2367</v>
       </c>
       <c r="S27" t="n">
-        <v>3.0091</v>
+        <v>3.795500000000001</v>
       </c>
       <c r="T27" t="n">
-        <v>-0.1143000000000003</v>
+        <v>-0.1143999999999999</v>
       </c>
       <c r="U27" t="n">
-        <v>3.123499999999999</v>
+        <v>3.9098</v>
       </c>
       <c r="V27" t="n">
         <v>-3.0748</v>
